--- a/ゲーム科2年/00_前期/ゲーム開発Ⅱ/スケジュール.xlsx
+++ b/ゲーム科2年/00_前期/ゲーム開発Ⅱ/スケジュール.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kic-admin\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ArakiYusuke\Textbook\ゲーム科2年\00_前期\ゲーム開発Ⅱ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EFE068C-3A05-4DA6-9234-0DDEEB4239DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0ABDAC15-C1B9-4D47-BB28-BD7EA42D45FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A0BA4298-C2C7-4C54-BB3A-0BA7CD3DD91A}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="18">
   <si>
     <t>5月</t>
     <rPh sb="1" eb="2">
@@ -54,27 +54,10 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>企画＆仕様確定</t>
-    <rPh sb="0" eb="2">
-      <t>キカク</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>シヨウ</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>カクテイ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>6月</t>
     <rPh sb="1" eb="2">
       <t>ガツ</t>
     </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>マイルストーン</t>
     <phoneticPr fontId="2"/>
   </si>
   <si>
@@ -156,6 +139,31 @@
   </si>
   <si>
     <t>マスターアップ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>キックオフ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>進捗確認</t>
+    <rPh sb="0" eb="4">
+      <t>シンチョクカクニン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>α版</t>
+    <rPh sb="1" eb="2">
+      <t>バン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>10/1進捗確認</t>
+    <rPh sb="4" eb="8">
+      <t>シンチョクカクニン</t>
+    </rPh>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -981,8 +989,9 @@
       <c r="AF8" s="9"/>
     </row>
     <row r="9" spans="1:32" x14ac:dyDescent="0.4">
-      <c r="W9" s="10" t="s">
-        <v>1</v>
+      <c r="W9" s="12"/>
+      <c r="AA9" s="10" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -1004,7 +1013,7 @@
   <sheetData>
     <row r="1" spans="1:31" s="1" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:31" s="6" customFormat="1" x14ac:dyDescent="0.4">
@@ -1299,13 +1308,13 @@
     </row>
     <row r="9" spans="1:31" x14ac:dyDescent="0.4">
       <c r="P9" s="15" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Q9" s="14"/>
       <c r="R9" s="14"/>
       <c r="W9" s="12"/>
       <c r="AE9" s="10" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -1327,7 +1336,7 @@
   <sheetData>
     <row r="1" spans="1:32" s="1" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:32" s="6" customFormat="1" x14ac:dyDescent="0.4">
@@ -1419,7 +1428,7 @@
       <c r="AD2" s="5">
         <v>29</v>
       </c>
-      <c r="AE2" s="2">
+      <c r="AE2" s="5">
         <v>30</v>
       </c>
       <c r="AF2" s="2">
@@ -1630,11 +1639,13 @@
       <c r="AF8" s="9"/>
     </row>
     <row r="9" spans="1:32" x14ac:dyDescent="0.4">
-      <c r="W9" s="12"/>
-      <c r="AE9" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="AF9" s="15"/>
+      <c r="W9" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="AE9" s="12"/>
+      <c r="AF9" s="15" t="s">
+        <v>4</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2"/>
@@ -1655,7 +1666,7 @@
   <sheetData>
     <row r="1" spans="1:32" s="1" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:32" s="6" customFormat="1" x14ac:dyDescent="0.4">
@@ -1959,7 +1970,7 @@
     </row>
     <row r="9" spans="1:32" x14ac:dyDescent="0.4">
       <c r="B9" s="15" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C9" s="14"/>
       <c r="D9" s="14"/>
@@ -2001,7 +2012,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{004AD2DB-5ABE-424B-B4EA-4E7F668C29F1}">
-  <dimension ref="A1:AE9"/>
+  <dimension ref="A1:AF9"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
@@ -2009,12 +2020,12 @@
     <col min="32" max="57" width="3.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" s="1" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:32" s="1" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:31" s="6" customFormat="1" x14ac:dyDescent="0.4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:32" s="6" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A2" s="3"/>
       <c r="B2" s="4">
         <v>1</v>
@@ -2107,7 +2118,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:32" x14ac:dyDescent="0.4">
       <c r="A3" s="7"/>
       <c r="B3" s="8"/>
       <c r="C3" s="8"/>
@@ -2140,7 +2151,7 @@
       <c r="AD3" s="9"/>
       <c r="AE3" s="9"/>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:32" x14ac:dyDescent="0.4">
       <c r="A4" s="7"/>
       <c r="B4" s="8"/>
       <c r="C4" s="8"/>
@@ -2172,7 +2183,7 @@
       <c r="AD4" s="9"/>
       <c r="AE4" s="9"/>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.4">
       <c r="A5" s="7"/>
       <c r="B5" s="8"/>
       <c r="C5" s="8"/>
@@ -2205,7 +2216,7 @@
       <c r="AD5" s="9"/>
       <c r="AE5" s="9"/>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.4">
       <c r="A6" s="7"/>
       <c r="B6" s="8"/>
       <c r="C6" s="8"/>
@@ -2238,7 +2249,7 @@
       <c r="AD6" s="9"/>
       <c r="AE6" s="9"/>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.4">
       <c r="A7" s="7"/>
       <c r="B7" s="8"/>
       <c r="C7" s="8"/>
@@ -2271,7 +2282,7 @@
       <c r="AD7" s="9"/>
       <c r="AE7" s="9"/>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.4">
       <c r="A8" s="7"/>
       <c r="B8" s="8"/>
       <c r="C8" s="8"/>
@@ -2304,7 +2315,7 @@
       <c r="AD8" s="9"/>
       <c r="AE8" s="9"/>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:32" x14ac:dyDescent="0.4">
       <c r="B9" s="12"/>
       <c r="C9" s="16"/>
       <c r="D9" s="16"/>
@@ -2334,8 +2345,9 @@
       <c r="AB9" s="16"/>
       <c r="AC9" s="16"/>
       <c r="AD9" s="16"/>
-      <c r="AE9" s="10" t="s">
-        <v>3</v>
+      <c r="AE9" s="12"/>
+      <c r="AF9" s="10" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -2357,7 +2369,7 @@
   <sheetData>
     <row r="1" spans="1:32" s="1" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:32" s="6" customFormat="1" x14ac:dyDescent="0.4">
@@ -2660,7 +2672,9 @@
       <c r="AF8" s="9"/>
     </row>
     <row r="9" spans="1:32" x14ac:dyDescent="0.4">
-      <c r="B9" s="12"/>
+      <c r="B9" s="10" t="s">
+        <v>15</v>
+      </c>
       <c r="C9" s="16"/>
       <c r="D9" s="16"/>
       <c r="E9" s="16"/>
@@ -2689,9 +2703,7 @@
       <c r="AB9" s="16"/>
       <c r="AC9" s="16"/>
       <c r="AD9" s="16"/>
-      <c r="AE9" s="10" t="s">
-        <v>3</v>
-      </c>
+      <c r="AE9" s="12"/>
       <c r="AF9" s="12"/>
     </row>
   </sheetData>
@@ -2713,7 +2725,7 @@
   <sheetData>
     <row r="1" spans="1:31" s="1" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:31" s="6" customFormat="1" x14ac:dyDescent="0.4">
@@ -2805,7 +2817,7 @@
       <c r="AD2" s="2">
         <v>29</v>
       </c>
-      <c r="AE2" s="2">
+      <c r="AE2" s="5">
         <v>30</v>
       </c>
     </row>
@@ -3011,7 +3023,9 @@
       <c r="C9" s="16"/>
       <c r="D9" s="16"/>
       <c r="E9" s="16"/>
-      <c r="F9" s="16"/>
+      <c r="F9" s="10" t="s">
+        <v>12</v>
+      </c>
       <c r="G9" s="16"/>
       <c r="H9" s="16"/>
       <c r="I9" s="16"/>
@@ -3036,9 +3050,7 @@
       <c r="AB9" s="16"/>
       <c r="AC9" s="16"/>
       <c r="AD9" s="16"/>
-      <c r="AE9" s="15" t="s">
-        <v>11</v>
-      </c>
+      <c r="AE9" s="12"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2"/>
@@ -3059,7 +3071,7 @@
   <sheetData>
     <row r="1" spans="1:31" s="1" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:31" s="6" customFormat="1" x14ac:dyDescent="0.4">
@@ -3354,7 +3366,7 @@
     </row>
     <row r="9" spans="1:31" x14ac:dyDescent="0.4">
       <c r="B9" s="15" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C9" s="14"/>
       <c r="D9" s="14"/>
@@ -3405,7 +3417,7 @@
   <sheetData>
     <row r="1" spans="1:32" s="1" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:32" s="6" customFormat="1" x14ac:dyDescent="0.4">
@@ -3709,7 +3721,7 @@
     </row>
     <row r="9" spans="1:32" x14ac:dyDescent="0.4">
       <c r="B9" s="15" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C9" s="14"/>
       <c r="D9" s="14"/>
@@ -3724,13 +3736,13 @@
       <c r="M9" s="16"/>
       <c r="N9" s="16"/>
       <c r="O9" s="16"/>
-      <c r="P9" s="10" t="s">
-        <v>14</v>
-      </c>
+      <c r="P9" s="12"/>
       <c r="Q9" s="16"/>
       <c r="R9" s="16"/>
       <c r="S9" s="16"/>
-      <c r="T9" s="16"/>
+      <c r="T9" s="10" t="s">
+        <v>13</v>
+      </c>
       <c r="U9" s="16"/>
       <c r="V9" s="16"/>
       <c r="W9" s="12"/>
@@ -3740,9 +3752,7 @@
       <c r="AA9" s="16"/>
       <c r="AB9" s="16"/>
       <c r="AC9" s="16"/>
-      <c r="AD9" s="10" t="s">
-        <v>15</v>
-      </c>
+      <c r="AD9" s="12"/>
       <c r="AE9" s="12"/>
       <c r="AF9" s="12"/>
     </row>
@@ -3754,6 +3764,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="26553de7-2a3a-444c-a024-df4cb947fd03" xsi:nil="true"/>
@@ -3762,15 +3781,6 @@
     </lcf76f155ced4ddcb4097134ff3c332f>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3969,20 +3979,20 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DDC1435B-6AB6-4AB2-8181-7AB2A8D90409}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FB4AC433-DB2B-4AE9-979C-606A42CB94A1}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="26553de7-2a3a-444c-a024-df4cb947fd03"/>
     <ds:schemaRef ds:uri="c0d4a769-b4b6-44f5-bafd-bfbeb89b0b0c"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DDC1435B-6AB6-4AB2-8181-7AB2A8D90409}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/ゲーム科2年/00_前期/ゲーム開発Ⅱ/スケジュール.xlsx
+++ b/ゲーム科2年/00_前期/ゲーム開発Ⅱ/スケジュール.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ArakiYusuke\Textbook\ゲーム科2年\00_前期\ゲーム開発Ⅱ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0ABDAC15-C1B9-4D47-BB28-BD7EA42D45FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00864992-2492-4026-9D48-023FA80EDDCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A0BA4298-C2C7-4C54-BB3A-0BA7CD3DD91A}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="20">
   <si>
     <t>5月</t>
     <rPh sb="1" eb="2">
@@ -163,6 +163,20 @@
     <t>10/1進捗確認</t>
     <rPh sb="4" eb="8">
       <t>シンチョクカクニン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>企画〆</t>
+    <rPh sb="0" eb="2">
+      <t>キカク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>仕様＆スケジュール〆</t>
+    <rPh sb="0" eb="2">
+      <t>シヨウ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -1307,11 +1321,17 @@
       <c r="AE8" s="9"/>
     </row>
     <row r="9" spans="1:31" x14ac:dyDescent="0.4">
+      <c r="F9" s="1" t="s">
+        <v>18</v>
+      </c>
       <c r="P9" s="15" t="s">
         <v>3</v>
       </c>
       <c r="Q9" s="14"/>
       <c r="R9" s="14"/>
+      <c r="T9" s="1" t="s">
+        <v>19</v>
+      </c>
       <c r="W9" s="12"/>
       <c r="AE9" s="10" t="s">
         <v>15</v>
@@ -3764,26 +3784,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="26553de7-2a3a-444c-a024-df4cb947fd03" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c0d4a769-b4b6-44f5-bafd-bfbeb89b0b0c">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x0101005F0D9E193D28814892BA96752E68B42F" ma:contentTypeVersion="11" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="7ef2c4f7c5cf37d6221d7b1dda883374">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c0d4a769-b4b6-44f5-bafd-bfbeb89b0b0c" xmlns:ns3="26553de7-2a3a-444c-a024-df4cb947fd03" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="725cefcd41332f88909580cd13155635" ns2:_="" ns3:_="">
     <xsd:import namespace="c0d4a769-b4b6-44f5-bafd-bfbeb89b0b0c"/>
@@ -3978,10 +3978,41 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="26553de7-2a3a-444c-a024-df4cb947fd03" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c0d4a769-b4b6-44f5-bafd-bfbeb89b0b0c">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DDC1435B-6AB6-4AB2-8181-7AB2A8D90409}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{974AEB67-0EB4-422A-8375-3AEC86DF31AC}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="c0d4a769-b4b6-44f5-bafd-bfbeb89b0b0c"/>
+    <ds:schemaRef ds:uri="26553de7-2a3a-444c-a024-df4cb947fd03"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -3998,20 +4029,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{974AEB67-0EB4-422A-8375-3AEC86DF31AC}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DDC1435B-6AB6-4AB2-8181-7AB2A8D90409}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="c0d4a769-b4b6-44f5-bafd-bfbeb89b0b0c"/>
-    <ds:schemaRef ds:uri="26553de7-2a3a-444c-a024-df4cb947fd03"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>